--- a/Noticias_Calcario_20260718.xlsx
+++ b/Noticias_Calcario_20260718.xlsx
@@ -463,22 +463,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Niebla Swimming Pools - 5 - ArchDaily</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/07/2026 01:45</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSFVHMV9GYzJhZzh6Vnh6cEduLUFIcW9JM0liMEdGV1ZsOUdCMmpQWDNFaWlWRnZpUUQ3TjhwVTQ4UkRrZk9WY3JfeXpFMVQ3U1F3aUh0ZUNIOXlsdGFpTldJXzh3dmc3dHIza21iV0laZmhNbTUzUDFWbkxMdU5tRndxQnVCZVU1SjF4Z3VPNm5BMjRoR0lTTmlXbFpjZGhHM0V2YlBfZGEzMUlmOU9wdFp2NFBBSHBZS2w1UDZoUmwtMWJ5RjZXdXh6MV9mYUpsYnB1V19FclFnUjNSSmx5bW9CaldBSFhOVjJ5UW1zLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
         </is>
       </c>
     </row>
@@ -749,56 +749,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Galeria de Porcelain Mosaics – Olympic Series - 4 - ArchDaily</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16/07/2026 18:02</t>
+          <t>16/07/2026 17:18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNaUw5R1NLTUlpMWxBYmhvVWN5V1hUaVJjTVJXTHJwajg4UTN6bThCSXMybkhVTjZ5WGw0T2N1SUNpOUFybnFJaEN6Q1NKOF95R2JSNjdCTU1oVmlLOU96cjNFdGJfWEpBY0dJSXVPY1ZOSlZDLVo5c3U0SGdCYTExdlpmY0dOY3E4YmxHSDlLUVpsanJSY0FMN3JSaHFZclBmeTkxWlJFRHR5TExpU3R4d0dhcW1fcm9VV0FnSGFFYjRONkNfSkVOTll1VXBLa3VfcnRoMlRYR2pkOFFUTFljZFd0UEhGN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16/07/2026 17:18</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,315 +808,315 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
+          <t>Queda da ureia melhora poder de compra, mas fosfatados ainda preocupam - boca.com.br</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 15:22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkdGck5rMVc3aHBKRkVTVDY1YjhUVWdfenJCV3dBVGdVTlhkZmlNcVhFdkVnUUkwQURQMklOTVpXeGJyaHFvRUxEZDg4RUlGV1hzUl9QWElBYWRRcllDc3hEb1pKZkcxa0UzZlNnUnZULTFsWjZrLW9HbzJEbDBwU21Kd2xLaDljRFR5ZGEtXzhBNHpGLTJuOTRLbXNRX3BDZ0Vv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Queda da ureia melhora poder de compra, mas fosfatados ainda preocupam - boca.com.br</t>
+          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16/07/2026 15:22</t>
+          <t>16/07/2026 14:55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkdGck5rMVc3aHBKRkVTVDY1YjhUVWdfenJCV3dBVGdVTlhkZmlNcVhFdkVnUUkwQURQMklOTVpXeGJyaHFvRUxEZDg4RUlGV1hzUl9QWElBYWRRcllDc3hEb1pKZkcxa0UzZlNnUnZULTFsWjZrLW9HbzJEbDBwU21Kd2xLaDljRFR5ZGEtXzhBNHpGLTJuOTRLbXNRX3BDZ0Vv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbWdlQXVxd2NvZFN4S0JDUjloZ3BieERuX0NjUlVOUkNPU2loOFFaM0pLd3YyQ0NnajRnM1BTRURWYVY0cFpwNnpjN1o1NTA0TVlGYnhvZ0E3S1AyRWd3aXA5MmUxbm1aS2FETVhSYnNmbUFrUThIYlA5QzhMbV9tT0pyc3F0RVF0RnBrLUdTMWQ4dG5OUlNwemVaRmZpbnFsSllVbWZZZnBnbldO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 3 - ArchDaily</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16/07/2026 14:55</t>
+          <t>16/07/2026 14:06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbWdlQXVxd2NvZFN4S0JDUjloZ3BieERuX0NjUlVOUkNPU2loOFFaM0pLd3YyQ0NnajRnM1BTRURWYVY0cFpwNnpjN1o1NTA0TVlGYnhvZ0E3S1AyRWd3aXA5MmUxbm1aS2FETVhSYnNmbUFrUThIYlA5QzhMbV9tT0pyc3F0RVF0RnBrLUdTMWQ4dG5OUlNwemVaRmZpbnFsSllVbWZZZnBnbldO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16/07/2026 14:06</t>
+          <t>16/07/2026 14:01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2729ad43bcae3456bc452d6c6f&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16/07/2026 14:01</t>
+          <t>16/07/2026 13:33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b6ff8f645388743f47183998420&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16/07/2026 13:33</t>
+          <t>16/07/2026 13:21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
+          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16/07/2026 13:21</t>
+          <t>16/07/2026 12:09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 6 - ArchDaily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16/07/2026 12:09</t>
+          <t>16/07/2026 11:18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOUlFaaTNyTW1RaGNGYll5c25QOVFsc1NNdGhsNzhEWUo4ckJacTYtYS05MDJPeURGOVRNTVY0NW5xOGZhcFZxTmg1ODVTd1l4TzZKR0Z1TzBlUUhKVFVrN1QtbnNzUXhiMWY4RXBsMzhCZlc2Um8zanYyRGNvQk41alpHNGl5VlBIM09qLXgya3hRRmVpaEVZVVgtSHZyeHZZbThVOW03VlJiZmhNWkllX0xTY3l1MjFTcHI4eWNVc292S2tWS1V0UkVtS1BUZnJkR05EMEpIc0FMSERGXzVjeGNLcThBUWxiRTAxWFhiUmlpMmF6cG8tOWNnTXNaeFdJa18tdUdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 6 - ArchDaily</t>
+          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16/07/2026 11:18</t>
+          <t>16/07/2026 11:16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOUlFaaTNyTW1RaGNGYll5c25QOVFsc1NNdGhsNzhEWUo4ckJacTYtYS05MDJPeURGOVRNTVY0NW5xOGZhcFZxTmg1ODVTd1l4TzZKR0Z1TzBlUUhKVFVrN1QtbnNzUXhiMWY4RXBsMzhCZlc2Um8zanYyRGNvQk41alpHNGl5VlBIM09qLXgya3hRRmVpaEVZVVgtSHZyeHZZbThVOW03VlJiZmhNWkllX0xTY3l1MjFTcHI4eWNVc292S2tWS1V0UkVtS1BUZnJkR05EMEpIc0FMSERGXzVjeGNLcThBUWxiRTAxWFhiUmlpMmF6cG8tOWNnTXNaeFdJa18tdUdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16/07/2026 11:16</t>
+          <t>16/07/2026 10:25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNMTVOXzVPNXhnSmZNUnJHQXlabGw1RFVZYkxzLTNoSmxEWllHSzBPSG52bWg2UVdRRUp0eEk5ODdGbDJaX0psUzk4RHYzb1FRMkF2eEh6dTNsTXcxLWNILUdwOF9mQk82TV9zX0V5Tnpnam9jTzhfQWJJRi1jcUk0c0pxRG5icUtSdWRJMWxLNldLbmZsdWJZV3dBbzN1S3RTYkpIZEROZWJ0UmNM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16/07/2026 10:25</t>
+          <t>16/07/2026 09:14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNMTVOXzVPNXhnSmZNUnJHQXlabGw1RFVZYkxzLTNoSmxEWllHSzBPSG52bWg2UVdRRUp0eEk5ODdGbDJaX0psUzk4RHYzb1FRMkF2eEh6dTNsTXcxLWNILUdwOF9mQk82TV9zX0V5Tnpnam9jTzhfQWJJRi1jcUk0c0pxRG5icUtSdWRJMWxLNldLbmZsdWJZV3dBbzN1S3RTYkpIZEROZWJ0UmNM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16/07/2026 09:14</t>
+          <t>16/07/2026 06:49</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNWFFMUTRpZHJ3QjRFY3RzSkJiNHhpYnhXX2J0ZVk2Sk1XNEZ5OTFsbmFVekhtR1E5MDd2a2tJdzdFWE1CNUVpczl4cHRDQlp4aHhhbkJtRzhlajhlRU1lTUs1ZXRsdWhTdXN0Wko1em9VUzNqamFCSXBJSmxQUmRVUjJMNlhOWDJ1ZEN6RzNqNEYzdXVIZFlMRnhQNHdBZm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
+          <t>Prevê-se que os preços globais da ureia permaneçam elevados, podendo duplicar os lucros da Ca Mau Fertilizer (DCM) este ano. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16/07/2026 06:49</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMVhIc1NkVGp5Vi1SclM2Yldza3djbXF2UnJsU0NNXzdhVjIwUXFVUzA0S3ZrTmlzdnNhNUdrQmIwUmtaVUthcGI3ZGUwLUt6MEMtUTZNSmUwQndfQ2Q3ZnF0SjlvTVBLOFFOZldiSnFlQTBqVzl5bGt6ekVyaUJpcmc1ZGlWWUVNVk8td0VUTHpiX0FRRTdUOEdIRVYyRjNN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Prevê-se que os preços globais da ureia permaneçam elevados, podendo duplicar os lucros da Ca Mau Fertilizer (DCM) este ano. - Vietnam.vn</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 02:55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMVhIc1NkVGp5Vi1SclM2Yldza3djbXF2UnJsU0NNXzdhVjIwUXFVUzA0S3ZrTmlzdnNhNUdrQmIwUmtaVUthcGI3ZGUwLUt6MEMtUTZNSmUwQndfQ2Q3ZnF0SjlvTVBLOFFOZldiSnFlQTBqVzl5bGt6ekVyaUJpcmc1ZGlWWUVNVk8td0VUTHpiX0FRRTdUOEdIRVYyRjNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1128,83 +1128,83 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
+          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16/07/2026 02:55</t>
+          <t>16/07/2026 01:37</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPM2loYUlCdFdlejZrU1o1aWNuSlBWNTJ1T2gxTjdqN2lqQlctbEd0Vm5scGlZYUZTQ2xzejVOYVl0RUVZd3VxZFFaNkxvZFllenlyUzktdUtZSWNHRUJtTlBHRFFQQ19yX1RReVRYdDRLeDFxLVRBaHFfVk1tWENJZEJJRWpWWXdaNTBWczdVOFNLS3NaODhTVWhSZlJiNnNxek1ZZVdPYjdUdS1vVXhVRldtSUlMalpDODlZWDhpNnpXX1M0c1g3bFk4b1pCdXhfREkyQktfeUZKd1RlUHEwUlB0YUcydTVGX3RR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 4 - ArchDaily</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16/07/2026 01:37</t>
+          <t>15/07/2026 20:03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPM2loYUlCdFdlejZrU1o1aWNuSlBWNTJ1T2gxTjdqN2lqQlctbEd0Vm5scGlZYUZTQ2xzejVOYVl0RUVZd3VxZFFaNkxvZFllenlyUzktdUtZSWNHRUJtTlBHRFFQQ19yX1RReVRYdDRLeDFxLVRBaHFfVk1tWENJZEJJRWpWWXdaNTBWczdVOFNLS3NaODhTVWhSZlJiNnNxek1ZZVdPYjdUdS1vVXhVRldtSUlMalpDODlZWDhpNnpXX1M0c1g3bFk4b1pCdXhfREkyQktfeUZKd1RlUHEwUlB0YUcydTVGX3RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
+          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15/07/2026 20:03</t>
+          <t>15/07/2026 19:35</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - Notícias ao Minuto Brasil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15/07/2026 19:35</t>
+          <t>15/07/2026 18:11</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNk9oVWZycVZaTy1oVlZoZl91VnE1U0tINURDVk1MeG0ydUNUMnY0dmJ2Tk1pc3h6ZTB6aGZ3UUpIRTF5dDQyenpMTzB3VDBfOUJJUVkzcWwzTFRBTUlSUEd5a2NsODZ0QUQ0VjZacC1BWnI3dVFNb3l0ejBVVk5HVGd2RjZEcng0LXlnT2pmcmExUVVlODFXUjB4akFKZnFBc19sRlpKcThZUmtpdTZCVS1EN3RzUW9rUDRyamZJWWh5QXlxRUR3dG5MTTNvWExVa1N6TnJSdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1216,61 +1216,61 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - Notícias ao Minuto Brasil</t>
+          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15/07/2026 18:11</t>
+          <t>15/07/2026 16:45</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNk9oVWZycVZaTy1oVlZoZl91VnE1U0tINURDVk1MeG0ydUNUMnY0dmJ2Tk1pc3h6ZTB6aGZ3UUpIRTF5dDQyenpMTzB3VDBfOUJJUVkzcWwzTFRBTUlSUEd5a2NsODZ0QUQ0VjZacC1BWnI3dVFNb3l0ejBVVk5HVGd2RjZEcng0LXlnT2pmcmExUVVlODFXUjB4akFKZnFBc19sRlpKcThZUmtpdTZCVS1EN3RzUW9rUDRyamZJWWh5QXlxRUR3dG5MTTNvWExVa1N6TnJSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15/07/2026 16:45</t>
+          <t>15/07/2026 16:02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>Luana Piovani ataca Virginia Fonseca na web e diz sentir "cheiro de enxofre" - RedeTV!</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15/07/2026 16:02</t>
+          <t>15/07/2026 15:47</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeElPQURYRFNpd3kwclhTbnFRQTFOMzNTcGE0OHdZRDk0R1Q4bG1EbHg0aWw3cDRvUmdHZ0dsSFBWby1tbm5IYlhhWTVlVzNTa284QkFRZVpKd3dVbVNHb1NRTGhNbGppSW5OQktkTlR3azRGYURteVNxVnZvLU1lMDNmMmJCVmZKS1pKVnRJRHpTSVdyUXZDRWRCc0IwbjFjTEFOY2dBNkFfTFF5QlBaTTNhNU1Fb2JvRkl3VXZWUnJMVy1aZnNSQtIBzwFBVV95cUxPWjlYY3V2VXZsekpsaFBRSTR5RkdnSk93clNDS0NLdGdzeWd2ZnNMXzlvS0ZRS1UzT3FOOFV2TDdmYmhiWDFjdEpVTkVPMUdDVXFBQjdXRGZFeGdHZ3dOYU1qekFGSFl4aGFHNmZrSUNPSXBuRWctMWtGTGJRc2p2RExXd2NPN2xucy1tY21TNUstRE1nWi1IZDVtTGxEeTJLdFJnWWR6cmZXdVFTVEVQQk85QUE2cFRvVThCNU81dDY3Y3RidEwwQ054c0YtQlU?oc=5</t>
         </is>
       </c>
     </row>
@@ -1282,83 +1282,83 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Luana Piovani ataca Virginia Fonseca na web e diz sentir "cheiro de enxofre" - RedeTV!</t>
+          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15/07/2026 15:47</t>
+          <t>15/07/2026 15:41</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeElPQURYRFNpd3kwclhTbnFRQTFOMzNTcGE0OHdZRDk0R1Q4bG1EbHg0aWw3cDRvUmdHZ0dsSFBWby1tbm5IYlhhWTVlVzNTa284QkFRZVpKd3dVbVNHb1NRTGhNbGppSW5OQktkTlR3azRGYURteVNxVnZvLU1lMDNmMmJCVmZKS1pKVnRJRHpTSVdyUXZDRWRCc0IwbjFjTEFOY2dBNkFfTFF5QlBaTTNhNU1Fb2JvRkl3VXZWUnJMVy1aZnNSQtIBzwFBVV95cUxPWjlYY3V2VXZsekpsaFBRSTR5RkdnSk93clNDS0NLdGdzeWd2ZnNMXzlvS0ZRS1UzT3FOOFV2TDdmYmhiWDFjdEpVTkVPMUdDVXFBQjdXRGZFeGdHZ3dOYU1qekFGSFl4aGFHNmZrSUNPSXBuRWctMWtGTGJRc2p2RExXd2NPN2xucy1tY21TNUstRE1nWi1IZDVtTGxEeTJLdFJnWWR6cmZXdVFTVEVQQk85QUE2cFRvVThCNU81dDY3Y3RidEwwQ054c0YtQlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
+          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15/07/2026 15:41</t>
+          <t>15/07/2026 15:16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
+          <t>Galeria de Flooring Panels - Dietfurt Limestone - 14 - ArchDaily</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15/07/2026 15:16</t>
+          <t>15/07/2026 14:44</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPM3NhRlotVXRCZEZyX3l4Tkw1NnQycmMyTGhjSFdxeElZRmhDaVlpVzF1elBFU3pXbzdHU0hqdTMzd3U5RjlVRWcwUE41RVRCWUljMHFHeU9kX205SHlVOFhOQWtEcVhOUWZCWkRzQVI1NXg5V01HYk9BNHdWWHhqekNjMlBudnZRODhzT3VJU2NlelNvM0FJR2xselVDbUZYclpYa0RDQ2ZJUUxxUV9F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Galeria de Flooring Panels - Dietfurt Limestone - 14 - ArchDaily</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15/07/2026 14:44</t>
+          <t>15/07/2026 13:10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPM3NhRlotVXRCZEZyX3l4Tkw1NnQycmMyTGhjSFdxeElZRmhDaVlpVzF1elBFU3pXbzdHU0hqdTMzd3U5RjlVRWcwUE41RVRCWUljMHFHeU9kX205SHlVOFhOQWtEcVhOUWZCWkRzQVI1NXg5V01HYk9BNHdWWHhqekNjMlBudnZRODhzT3VJU2NlelNvM0FJR2xselVDbUZYclpYa0RDQ2ZJUUxxUV9F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
+          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15/07/2026 13:10</t>
+          <t>15/07/2026 12:35</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
         </is>
       </c>
     </row>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
+          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15/07/2026 12:35</t>
+          <t>15/07/2026 11:51</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
+          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>15/07/2026 11:51</t>
+          <t>15/07/2026 11:09</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
+          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>15/07/2026 11:09</t>
+          <t>15/07/2026 10:17</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1458,193 +1458,193 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
+          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15/07/2026 10:17</t>
+          <t>15/07/2026 08:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
+          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>15/07/2026 08:00</t>
+          <t>14/07/2026 23:07</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
+          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>14/07/2026 23:07</t>
+          <t>14/07/2026 22:11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily</t>
+          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>14/07/2026 22:11</t>
+          <t>14/07/2026 21:19</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
+          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>14/07/2026 21:19</t>
+          <t>14/07/2026 21:03</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>14/07/2026 21:03</t>
+          <t>14/07/2026 17:57</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>14/07/2026 17:57</t>
+          <t>14/07/2026 15:28</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
+          <t>Fertilizante em alerta - Olhar Direto</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14/07/2026 15:28</t>
+          <t>14/07/2026 15:27</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fertilizante em alerta - Olhar Direto</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>14/07/2026 15:27</t>
+          <t>14/07/2026 15:20</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b6ff8f645388743f47183998420&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2729ad43bcae3456bc452d6c6f&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2942,19 +2942,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b7618ab4dc48d0d6f08876e9b44&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2d979a4e98a46825906044abe5&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3712,19 +3712,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,19 +3800,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Petrobras retoma obras de fábrica de fertilizantes em MS com investimento de mais de R$ 5 bi - Canal Rural</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNc3VSSjllbUY2UW9zVHdkRzh0a1M5dDdqdGV2VWdjM3JUTWNUZm9PeTlES1p6b24xMDI3SHp2RnNmZHlUeTBrZ1I1WDVXaVBsdkphb3JMbkliNHQtUTV1RVUySGlEbnhBYmRUdFJwRHZoQ3piRlJqTTRrMXhwWFo0T0lTWHRfMVpUYUpQU1d0T0psYXpKVVJQT1pzT0lRTTZacURMSklXTktGMk9PRW1Xb0ZMT1B0SEZfMGRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Petrobras retoma obras de fábrica de fertilizantes em MS com investimento de mais de R$ 5 bi - Canal Rural</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNc3VSSjllbUY2UW9zVHdkRzh0a1M5dDdqdGV2VWdjM3JUTWNUZm9PeTlES1p6b24xMDI3SHp2RnNmZHlUeTBrZ1I1WDVXaVBsdkphb3JMbkliNHQtUTV1RVUySGlEbnhBYmRUdFJwRHZoQ3piRlJqTTRrMXhwWFo0T0lTWHRfMVpUYUpQU1d0T0psYXpKVVJQT1pzT0lRTTZacURMSklXTktGMk9PRW1Xb0ZMT1B0SEZfMGRr?oc=5</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,19 +4042,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,19 +4064,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4137,34 +4137,34 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>23/06/2026 07:31</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,19 +4174,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4262,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,19 +4284,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4306,19 +4306,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4394,19 +4394,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,19 +4416,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4658,19 +4658,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - topnews.com.br</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNcjh3V3ZvZHlXUDI2SThLcnhFRDVuTXZsVDV4ejZ1VW82NUo4T3VkZTU3MFRKeDlWNU8tNENuQ0Fza05Zdkh5QVl1X0lNNFA3MDZ4cU9RVjUyUUZFMVNDemZvY1dCSjlPb2xXeEx3ZDYxOFlncnptMDJfcE9paW5CNEVzRk5mUWpTWlQyQlNIak9ub3h1a0g5ZkhkZndhQ0d5dG5tTm1sTkNpeEtqNmNpTXo0R0w5MFp4RWo4Tg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
@@ -4797,34 +4797,34 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>O ‘apagão’ da ureia - VEJA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,19 +4856,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>O ‘apagão’ da ureia - VEJA</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,63 +4900,63 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,19 +4966,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,51 +5032,51 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>07/06/2026 23:34</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>07/06/2026 23:34</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5088,51 +5088,51 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>03/06/2026 14:22</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 tem jogos empatados nas semifinais - jornaldaregiao.com</t>
+          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>03/06/2026 14:22</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQM01FdlJEQnpyMGhkMDNTcWZZZTN2dGk4azUzdTRqVExKbjV4WExTSlgwVWQ4elY4TnluTHVwNzZCT3dkN1ZFWUlMbGxqNVZYdzVMMnNsRmtYVWJ0ZlVEN0lVcUxNNGU5WHY3QlN5dkRUdVA2dlpVVThPcG11UWpleF9WTXV0OWhmeFU5eQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Copa do Calcário 2026 tem jogos empatados nas semifinais - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQM01FdlJEQnpyMGhkMDNTcWZZZTN2dGk4azUzdTRqVExKbjV4WExTSlgwVWQ4elY4TnluTHVwNzZCT3dkN1ZFWUlMbGxqNVZYdzVMMnNsRmtYVWJ0ZlVEN0lVcUxNNGU5WHY3QlN5dkRUdVA2dlpVVThPcG11UWpleF9WTXV0OWhmeFU5eQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5154,29 +5154,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,41 +5186,41 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,19 +5230,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,19 +5296,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,29 +5318,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,63 +5384,63 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - jornalopcao.com.br</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,19 +5516,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,19 +5604,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5721,34 +5721,34 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>AGU fecha acordo de R$ 27 milhões por lavra ilegal de calcário - Jornal de Brasília</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPU0tZVWlMNUF1U1ZlWXE4a1I3cmhKT1JOWmZ2bFhpNVJkWkgzOGROUEJ5S3VRSEpqVVNpUHdTOGJoc0hIQ05OVmtob1g1Q1dVbTlic0o0MjhLYTRONUZtazBxN3UtYUJVaVB6bWhERHVmcjZZODJkak5UZDZqejdack5VdzVfaHR1X1hPVGRzVVlLeERtVU11bllOWGpmWHVpMmJLMEk4bmh1NkNhS0Rj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>AGU fecha acordo de R$ 27 milhões por lavra ilegal de calcário - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPU0tZVWlMNUF1U1ZlWXE4a1I3cmhKT1JOWmZ2bFhpNVJkWkgzOGROUEJ5S3VRSEpqVVNpUHdTOGJoc0hIQ05OVmtob1g1Q1dVbTlic0o0MjhLYTRONUZtazBxN3UtYUJVaVB6bWhERHVmcjZZODJkak5UZDZqejdack5VdzVfaHR1X1hPVGRzVVlLeERtVU11bllOWGpmWHVpMmJLMEk4bmh1NkNhS0Rj?oc=5</t>
         </is>
       </c>
     </row>
@@ -5770,29 +5770,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,19 +5802,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,19 +5846,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5990,51 +5990,51 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,19 +6044,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,19 +6066,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,29 +6088,29 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6139,34 +6139,34 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,19 +6198,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,19 +6220,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,19 +6242,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,29 +6264,29 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
@@ -6359,22 +6359,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense avançam às semifinais da Copa Calcário 2026 - Serra News</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE0wNncwaDFTai01LUpkUXFQU2Q2dFpUMDB2eGp3M3F6d01jU3RnSi1NR1ZpQmtiNGVObEFQUHhNS3l4VlExNWZ6MDlsQ3M0bEpIWmEteWNEWmRwb2hkd1pwY2ZjeTNmckhuYjJzangtZENxT2lIYTQtUGVoNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,19 +6726,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6748,19 +6748,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,19 +6770,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,19 +6792,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,19 +6814,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Vazamento de enxofre interdita rodovia Ayrton Senna, em São Paulo - band.com.br</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPYzM4TXRIamotWmZsZG83T0prMmNwb0ZRSnVFY3UxTEFqWnJIWVlmLW9Db3VzX1FSaURNN0RodkhTaGw2R0JkcHFIQWEwV2tPN2tUVnRVYzItUkNRUGQ0UFR4ZmZtWmJRbldEVzB1RWxzLVpfamZUUWVEdU9oZ2xMcHE5cFAtZVhvQXcxTjhERXcwWnJhenhjSmFfSk0wRUdJN184RlMwbEU5aWtHN0JOdmxUVXI1ZW1mZjBHUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia na Ansa e reforça estratégia no setor de fertilizantes - Exame</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNN2FLdVNOLVNmQ0NMUEhuTkF6bjEyQ3FnQXdxM2FoX21YcEtGdG5aZUh2MzNPa211NmlxY3BnMWVDMHFuUXVER3g4U3l6Q1VkS2pGbDAtMkZJenBlLXJFTnp4U2dqT3pyRTZkcUp0WFRZT2piVFVYNnJJZTNCd2VKSTBLeEJPbzhvS3UxdEV5eW96RVhiY2Z3OGdpZ2F3THV0dVR0MW9PRE5XRUl1bEhsYTlWN041NG1hY1VYdHVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Petrobras retoma produção de ureia na Ansa e reforça estratégia no setor de fertilizantes - Exame</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,19 +7078,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNN2FLdVNOLVNmQ0NMUEhuTkF6bjEyQ3FnQXdxM2FoX21YcEtGdG5aZUh2MzNPa211NmlxY3BnMWVDMHFuUXVER3g4U3l6Q1VkS2pGbDAtMkZJenBlLXJFTnp4U2dqT3pyRTZkcUp0WFRZT2piVFVYNnJJZTNCd2VKSTBLeEJPbzhvS3UxdEV5eW96RVhiY2Z3OGdpZ2F3THV0dVR0MW9PRE5XRUl1bEhsYTlWN041NG1hY1VYdHVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,19 +7166,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,19 +7298,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,51 +7452,51 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7525,34 +7525,34 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,19 +7584,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7606,19 +7606,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7628,63 +7628,63 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7723,12 +7723,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7738,51 +7738,51 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7794,83 +7794,83 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Macuco vence e lidera a Copa do Calcário - jornaldaregiao.com</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBja01USHVRZzB4dTBwSUtZWFNYU2I3eUU4VUF3eTA4N0V2WHVsM2gzdzBWVHQ5Z3V5aWQ2aHFJRzFNdFI1bGc4Tnh0ZWtaakRSSjJ5VHoycXVyaEZLbXdwVEM3TmhpbndoeVdscWlncG00NTI4MlVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,83 +7882,83 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7992,39 +7992,39 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8068,19 +8068,19 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,51 +8200,51 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Agricultores já acessaram mais de 80% da cota de calcário no Extremo Oeste - Rede Peperi</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPVnZNZFc2dnk0bEpPQ3gxZ1hIaVlnbktoWndsRGZEeFlEdXZTdzFUbVFRYS04TzRKb1NmZ0ZuOFhWZWdMN3ppc05vemlqdVV5MEczNGpaaUF1RW5RTDQ5bWctNHVyRmRURGdTbnpiZUcyUEhjOEtNQUNVa3N4ZEZnaE9jVEZWR0k4bXdQXy1xeTlmOE5nZ2JhQWQzTk5yZThYaFR3ZzZZZ0VORkpMYzZvXzl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,19 +8266,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Agricultores já acessaram mais de 80% da cota de calcário no Extremo Oeste - Rede Peperi</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8288,63 +8288,63 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPVnZNZFc2dnk0bEpPQ3gxZ1hIaVlnbktoWndsRGZEeFlEdXZTdzFUbVFRYS04TzRKb1NmZ0ZuOFhWZWdMN3ppc05vemlqdVV5MEczNGpaaUF1RW5RTDQ5bWctNHVyRmRURGdTbnpiZUcyUEhjOEtNQUNVa3N4ZEZnaE9jVEZWR0k4bXdQXy1xeTlmOE5nZ2JhQWQzTk5yZThYaFR3ZzZZZ0VORkpMYzZvXzl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,29 +8354,29 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8398,73 +8398,73 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8476,29 +8476,29 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8542,39 +8542,39 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8586,17 +8586,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
@@ -8608,51 +8608,51 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8674,17 +8674,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8706,19 +8706,19 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,19 +8750,19 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,29 +8772,29 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Copa do Calcário 2026 começa em abril - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1qMEZCUFBEOG9GWGpJSnluTy1EUFIwTmFOQVZXRmRWTWFSb19TU3llV0d1UUd6UEVRSV85SDBhbHFfdTg3STd4UzRYeHgzTkhrbzNMRFk5OW1YQVJFeHE2YXRJRVc2NmhKS2N6X2xQaHlUamM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8823,22 +8823,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - jornaldaregiao.com</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1qMEZCUFBEOG9GWGpJSnluTy1EUFIwTmFOQVZXRmRWTWFSb19TU3llV0d1UUd6UEVRSV85SDBhbHFfdTg3STd4UzRYeHgzTkhrbzNMRFk5OW1YQVJFeHE2YXRJRVc2NmhKS2N6X2xQaHlUamM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8872,61 +8872,61 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
@@ -8955,44 +8955,44 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>12/03/2026 04:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>12/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9043,56 +9043,56 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,41 +9102,41 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,51 +9146,51 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>04/03/2026 10:02</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9202,29 +9202,29 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>04/03/2026 10:02</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9268,29 +9268,29 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9300,29 +9300,29 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>28/02/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -9334,39 +9334,39 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>28/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9410,41 +9410,41 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,85 +9498,85 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
@@ -9598,17 +9598,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -9620,17 +9620,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9642,39 +9642,39 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9686,17 +9686,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
@@ -9730,29 +9730,29 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9835,12 +9835,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9850,19 +9850,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,19 +10312,19 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,19 +10400,19 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,19 +10444,19 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,19 +10510,19 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b71602f4bb5adf141a3692d44a1&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2951a14540a32a1e54d95fb77d&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -10891,66 +10891,66 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -10979,12 +10979,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
@@ -11006,17 +11006,17 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>18/11/2025 05:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -11028,39 +11028,39 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>18/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Mosaic Entra no Mercado de Fertirrigação, um Setor de 4 Milhões de Toneladas até 2030 - Forbes Brasil</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ1Z6amZ6SDBLNHYtOGtuMnZ5VnRCQ2lrYjNIQS1WcmdMZE9wZG9TRk80R3ZjWGc1dzE2RTF1LV9EOEdWXzk2LXhMY20yZlFZY2tLREZabFhnTUZhb2x3eEstZVYtcnlyMUdjZFVjTUFHdlF6bW5iMkozY29hUFl0bG5aXzRVbVZrTjB1d3QxR1hMeXBxUVpaeDNGQ0swREQtVFVaT2ZndTRQd2xUT2FRWnA0UEY0TWYzQVBYNjh0QlpoTV84OEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b71602f4bb5adf141a3692d44a1&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2951a14540a32a1e54d95fb77d&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b70561f407bb7032ed6141f8e2c&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2842674b80aa503ff1dd01d33a&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b5b71602f4bb5adf141a3692d44a1&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5b8a2951a14540a32a1e54d95fb77d&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>

--- a/Noticias_Calcario_20260718.xlsx
+++ b/Noticias_Calcario_20260718.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e0c6764874b8b427b43940bb1a&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a791054974b70808f1dd40d040&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e0c6764874b8b427b43940bb1a&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a791054974b70808f1dd40d040&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
@@ -2932,29 +2932,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mineradora CMOC terá que pagar R$ 11 milhões após contaminação ambiental em Catalão - Badiinho</t>
+          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>09/07/2026 12:50</t>
+          <t>09/07/2026 11:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9jQWwwVVZBV2pHcl94VzJPRV91UkNrUE1NM0FnVUdEMF9FOVBNemZSeDZIblVidnpkYllLZFIxNm5yTThNU1hUa2w1S0Y2bjhJSzBaNmtqNWZMVjRZdk0zak9MdHo5NDF6VkcxS1V5RFRvbHhB0gF6QVVfeXFMTVAwVjRIRVR0Vng1Y05rdjUxT05lU3p3UTl1MWt6NDRnandFcXMyeE1DelE1MVctMTR5eHloN0NsSlVYSVpZRTZvRFJnZnlickNPODNFVFRJSnBjRmVHZHV2cUtZM1N1Q2Y1M3NaU1BhbHA5V1pnaHpnMEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2976,83 +2976,83 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>09/07/2026 11:00</t>
+          <t>09/07/2026 10:56</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>09/07/2026 10:56</t>
+          <t>09/07/2026 06:50</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>09/07/2026 06:50</t>
+          <t>09/07/2026 06:15</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>09/07/2026 06:15</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>08/07/2026 20:25</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/07/2026 20:25</t>
+          <t>08/07/2026 18:08</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
+          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>08/07/2026 18:08</t>
+          <t>08/07/2026 14:33</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,61 +3196,61 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
+          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/07/2026 14:33</t>
+          <t>08/07/2026 11:33</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/07/2026 11:33</t>
+          <t>08/07/2026 11:07</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8adfe9747b48d5e1ad1f4460049&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/07/2026 11:07</t>
+          <t>08/07/2026 10:03</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e61a8a480f960f2a82be3c6d30&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3262,83 +3262,83 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/07/2026 10:03</t>
+          <t>08/07/2026 09:54</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/07/2026 09:54</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>07/07/2026 08:15</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - notícia marajó</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>07/07/2026 08:15</t>
+          <t>07/07/2026 06:18</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQamJYM082OHV1bmtldUhFVXR2ZTB0LXNmd21QMWZucllOMlVRaVhueFA3dWgtM2dlY2REcjFKLXdMU05PZGgwNFhkZm5WOTJiTDBlUjBNLXptd05fR0xDYzgtTExpTk51R2VVM3piU21IQ3N3RlJPUFJlWE92TFVpWEJzSDlhMGRMQ2MwanVNT05vM3B1VENXUHJKdjlhZ3BJNFZZSkdLd0U2dTZvSzh1T2EzaUExbmYxN2NDZFVfYUNIS1E1eDl0WUY3eks?oc=5</t>
         </is>
       </c>
     </row>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - notícia marajó</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>07/07/2026 06:18</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQamJYM082OHV1bmtldUhFVXR2ZTB0LXNmd21QMWZucllOMlVRaVhueFA3dWgtM2dlY2REcjFKLXdMU05PZGgwNFhkZm5WOTJiTDBlUjBNLXptd05fR0xDYzgtTExpTk51R2VVM3piU21IQ3N3RlJPUFJlWE92TFVpWEJzSDlhMGRMQ2MwanVNT05vM3B1VENXUHJKdjlhZ3BJNFZZSkdLd0U2dTZvSzh1T2EzaUExbmYxN2NDZFVfYUNIS1E1eDl0WUY3eks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,17 +3394,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Estação Livre MT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>06/07/2026 21:29</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWmFLanBDd0hKMG16cUM5MXJBRXJuc2dENlpiQ254SGN0ZS1rYXJQNXl5ZV95cm9oeDAxc0FzY3NwekZqMnkwNjBmSzRvYjc5NXkxcDVSUTRGZjV5bFVVbVpQOE94SU1wQmoyR1c2ZkhUdTRaQ2ctSEhxQUtsRzBKeG9FRWtwNVhlRVRnQ1FyS2dXNUx6ZGRPNlJ4VXZidVRKQ3BBWGI0UGhpN3paSDF6d2xjNUdmYy1OWXItUkpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3416,39 +3416,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Estação Livre MT</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>06/07/2026 21:29</t>
+          <t>06/07/2026 19:20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWmFLanBDd0hKMG16cUM5MXJBRXJuc2dENlpiQ254SGN0ZS1rYXJQNXl5ZV95cm9oeDAxc0FzY3NwekZqMnkwNjBmSzRvYjc5NXkxcDVSUTRGZjV5bFVVbVpQOE94SU1wQmoyR1c2ZkhUdTRaQ2ctSEhxQUtsRzBKeG9FRWtwNVhlRVRnQ1FyS2dXNUx6ZGRPNlJ4VXZidVRKQ3BBWGI0UGhpN3paSDF6d2xjNUdmYy1OWXItUkpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOSkQ1Q3FXZnhQcXhNSGVzSjlFNWVKMmNCdzk5Q1hZTFdmeE5BOVg2YXIxMDUyYVc3S1g3X2dTcmJqcEZzUUctS2RpNGdPZVN3a2xZNUhzNTBlQjNfdU45QVdta0R1NDl3MzdrdGtFR1QyNnUtV1JNMElHaU1ycnI2UGhBVzJ6NDdqREVFSVNBS2ljM2RwNlF0OFdIelUwcVVEeWYwMEZZSGswN3dOdi1LNHZVVTlqWjI3NS1qUTNRX1BIMzhVc1RPRkROcE5jQThpVmxZRVJYV3hJUVlHLVZ0RGRBdTlkOGxsOTljUkpLNlV4eGNlbTlOTGppejZwZTRRR3JQR2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Portal do Agronegócio</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>06/07/2026 19:20</t>
+          <t>06/07/2026 10:47</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOSkQ1Q3FXZnhQcXhNSGVzSjlFNWVKMmNCdzk5Q1hZTFdmeE5BOVg2YXIxMDUyYVc3S1g3X2dTcmJqcEZzUUctS2RpNGdPZVN3a2xZNUhzNTBlQjNfdU45QVdta0R1NDl3MzdrdGtFR1QyNnUtV1JNMElHaU1ycnI2UGhBVzJ6NDdqREVFSVNBS2ljM2RwNlF0OFdIelUwcVVEeWYwMEZZSGswN3dOdi1LNHZVVTlqWjI3NS1qUTNRX1BIMzhVc1RPRkROcE5jQThpVmxZRVJYV3hJUVlHLVZ0RGRBdTlkOGxsOTljUkpLNlV4eGNlbTlOTGppejZwZTRRR3JQR2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3460,149 +3460,149 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>06/07/2026 10:47</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
+          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>05/07/2026 16:45</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>05/07/2026 16:45</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>04/07/2026 01:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>04/07/2026 01:00</t>
+          <t>03/07/2026 10:20</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>03/07/2026 10:20</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3653,22 +3653,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>02/07/2026 17:01</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
         </is>
       </c>
     </row>
@@ -3680,95 +3680,95 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>02/07/2026 17:01</t>
+          <t>02/07/2026 04:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>02/07/2026 04:00</t>
+          <t>01/07/2026 10:48</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>01/07/2026 10:48</t>
+          <t>30/06/2026 18:22</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>30/06/2026 18:22</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3778,19 +3778,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>29/06/2026 08:22</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3844,29 +3844,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>29/06/2026 08:22</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3895,22 +3895,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3922,29 +3922,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,19 +3976,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
+          <t>Petrobras investe R$ 5 bilhões para reduzir importação de fertilizantes - Movimento Econômico</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>25/06/2026 04:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQeF9YQjU2alBQN01sYWUzY2VZRjJVeDBXOVI0bkpyYmxHaXVnVnR2aXRlUUtTNndLUkVOTTMtUFRfbmxsMGY0alZwUGMtakhCSm00c0ZXMldJR2ptQUE0VVM5VEtJOUJZY3R5eVF5ZG5TbVBrVDRIVXNROVF0Z0VaUF9xVUs3UXRsVm9VeEp1cHl3X1RXa1Nia3NjcnVmWVBQbEJhNHRaSlprOHpIaHZjQTlhQ1lMVGxab0U1clV1TEN1YnlOZEZj?oc=5</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Petrobras investe R$ 5 bilhões para reduzir importação de fertilizantes - Movimento Econômico</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,63 +4064,63 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQeF9YQjU2alBQN01sYWUzY2VZRjJVeDBXOVI0bkpyYmxHaXVnVnR2aXRlUUtTNndLUkVOTTMtUFRfbmxsMGY0alZwUGMtakhCSm00c0ZXMldJR2ptQUE0VVM5VEtJOUJZY3R5eVF5ZG5TbVBrVDRIVXNROVF0Z0VaUF9xVUs3UXRsVm9VeEp1cHl3X1RXa1Nia3NjcnVmWVBQbEJhNHRaSlprOHpIaHZjQTlhQ1lMVGxab0U1clV1TEN1YnlOZEZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>25/06/2026 04:00</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,19 +4130,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,41 +4152,41 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4247,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>22/06/2026 19:10</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4274,29 +4274,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>22/06/2026 19:10</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4379,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4423,34 +4423,34 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,51 +4460,51 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4516,29 +4516,29 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,51 +4548,51 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4621,34 +4621,34 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4658,19 +4658,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,95 +4680,95 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>12/06/2026 04:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>12/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>O ‘apagão’ da ureia - VEJA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>O ‘apagão’ da ureia - VEJA</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,63 +4856,63 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4922,19 +4922,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4944,19 +4944,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4995,44 +4995,44 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>07/06/2026 23:34</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>07/06/2026 23:34</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
         </is>
       </c>
     </row>
@@ -5083,34 +5083,34 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,41 +5120,41 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,29 +5318,29 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
@@ -5352,17 +5352,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,19 +5494,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,29 +5582,29 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5660,51 +5660,51 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,19 +5714,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5780,19 +5780,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,19 +5802,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,19 +5846,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,51 +5868,51 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5985,22 +5985,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
@@ -6029,22 +6029,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6342,51 +6342,51 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>16/05/2026 22:15</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>16/05/2026 22:15</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,51 +6396,51 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6452,17 +6452,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSFJIZGVZei1nU0tZTXdGeVdSekJlTkd5ajN1d3MwYk5LcmNTMlc1VWJXcjB3S2JGZmY4d2hTQnVBcGdBUjVYT3Z6Vnh0dVRrZFlXY1hEV25xWXBfVThpZkxFSGM4X3dvTjV6bWtMR2FHWTAwdElxNlpzV0RFNmxLMFhxbHRqUkxKNHdPODhMMEVBeHJfa1BpMGZ2a2FqbTQ5UVh1ZlJKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6513,56 +6513,56 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6594,19 +6594,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6689,44 +6689,44 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6777,44 +6777,44 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6843,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,17 +6914,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,17 +7068,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7090,17 +7090,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras retoma produção de ureia em fábrica no Paraná - Agência iNFRA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPYXZqc1RHdndMd21UaGhuNjJxal8ybGZldG5qQjduR2JhbDlOWTdGdlpHbnhaWjg1VmxCQUJxT05ScGk0OHU2aFNEcHFDNnJHRVVuSldZR0psOVNlYU1PZFR2SEZ3dWt1QjdHeUdKTU9pUG9OdklSbll2QjRsRkx4aFByOFlGTXJjQk82dmNsNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia em fábrica no Paraná - Agência iNFRA</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPYXZqc1RHdndMd21UaGhuNjJxal8ybGZldG5qQjduR2JhbDlOWTdGdlpHbnhaWjg1VmxCQUJxT05ScGk0OHU2aFNEcHFDNnJHRVVuSldZR0psOVNlYU1PZFR2SEZ3dWt1QjdHeUdKTU9pUG9OdklSbll2QjRsRkx4aFByOFlGTXJjQk82dmNsNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,51 +7298,51 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7371,34 +7371,34 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7408,19 +7408,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,19 +7430,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,19 +7452,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7474,63 +7474,63 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,51 +7584,51 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7640,73 +7640,73 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7728,17 +7728,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7767,34 +7767,34 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7838,17 +7838,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,19 +7980,19 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,51 +8046,51 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8112,63 +8112,63 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8178,29 +8178,29 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8229,66 +8229,66 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8300,29 +8300,29 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,19 +8332,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,51 +8354,51 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8410,17 +8410,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
@@ -8432,39 +8432,39 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8493,34 +8493,34 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,19 +8530,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,19 +8552,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8608,39 +8608,39 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8652,73 +8652,73 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,51 +8728,51 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>12/03/2026 04:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,19 +8794,19 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8816,63 +8816,63 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,41 +8882,41 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,51 +8926,51 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>04/03/2026 10:02</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8982,29 +8982,29 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>04/03/2026 10:02</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,19 +9014,19 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,41 +9036,41 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9080,29 +9080,29 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>28/02/2026 05:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -9114,39 +9114,39 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>28/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic anuncia resultados de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9190,41 +9190,41 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Mosaic anuncia resultados de 2025 - Revista Cultivar</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9234,19 +9234,19 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9256,19 +9256,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9278,85 +9278,85 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9366,29 +9366,29 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -9400,17 +9400,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9422,39 +9422,39 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9466,17 +9466,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,17 +9510,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9542,85 +9542,85 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9630,19 +9630,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9652,41 +9652,41 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9708,17 +9708,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9740,29 +9740,29 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>21/01/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcmlUZDBXN0szYV81b3IyR193M0xrNks3X01wdmhSdjRNRi1DNVgyWGxlZThqU1ZjVVM4bEczaHpJMllVX0lTNjNoYXZNREhJUEhhSGhYRWUyS1pSZnZmcmRCS1d5aHNZeWhJcmdYdlQ2eUZobmRkYXlXY29Od25wU1dPSXRCeXVGVlRqY3Q4RWI5N210THNuSWxZRmVTWDBPLVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
+          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9784,51 +9784,51 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcmlUZDBXN0szYV81b3IyR193M0xrNks3X01wdmhSdjRNRi1DNVgyWGxlZThqU1ZjVVM4bEczaHpJMllVX0lTNjNoYXZNREhJUEhhSGhYRWUyS1pSZnZmcmRCS1d5aHNZeWhJcmdYdlQ2eUZobmRkYXlXY29Od25wU1dPSXRCeXVGVlRqY3Q4RWI5N210THNuSWxZRmVTWDBPLVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
+          <t>Agricultores familiares podem se inscrever para receber calcário com subsídio em Santa Cruz; veja detalhes - Portal Arauto</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>21/01/2026 05:00</t>
+          <t>20/01/2026 05:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNTEp5WElac20xZW83c3RYX2hoY25tWTVLdHl6aU50ZWphQTN2eGEtTkktSFgyVzJkcHJYQXV2eDc4NThjZjNQaURKaGp5WjdCd05VeDlyVzFRaEgtRlVLZXZpVnlHb3BlVEhrODYxNndYRFNVNXViemhNc1M5MDFJbUJDazBGTmhaYndqeEhxTDRwY2RSb2R6bkNJOHBpYzNYa0RSNF9oMVBlUHdZWVNzb3lHamUya2c0Qm9oSEtTMnBfZ3p1ekZVOG93LWxKS2FUUWJUZWtrVGt3YVpqUUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Agricultores familiares podem se inscrever para receber calcário com subsídio em Santa Cruz; veja detalhes - Portal Arauto</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>20/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNTEp5WElac20xZW83c3RYX2hoY25tWTVLdHl6aU50ZWphQTN2eGEtTkktSFgyVzJkcHJYQXV2eDc4NThjZjNQaURKaGp5WjdCd05VeDlyVzFRaEgtRlVLZXZpVnlHb3BlVEhrODYxNndYRFNVNXViemhNc1M5MDFJbUJDazBGTmhaYndqeEhxTDRwY2RSb2R6bkNJOHBpYzNYa0RSNF9oMVBlUHdZWVNzb3lHamUya2c0Qm9oSEtTMnBfZ3p1ekZVOG93LWxKS2FUUWJUZWtrVGt3YVpqUUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9872,29 +9872,29 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9906,39 +9906,39 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
@@ -9950,61 +9950,61 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>24/12/2025 17:01</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10016,61 +10016,61 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>24/12/2025 17:01</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>19/12/2025 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>19/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,41 +10180,41 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10246,19 +10246,19 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10268,19 +10268,19 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,19 +10290,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,29 +10312,29 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,17 +10544,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,73 +10588,73 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>12/12/2025 05:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>12/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a97a404f80b40ea5f8575e2e52&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e2b2b2404a8b9dc3c6cd2d96ed&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10664,73 +10664,73 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,17 +10742,17 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,19 +10774,19 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,29 +10796,29 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>18/11/2025 05:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10830,227 +10830,227 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>18/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>10/11/2025 05:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>10/11/2025 05:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a97a404f80b40ea5f8575e2e52&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>17/10/2025 04:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e2b2b2404a8b9dc3c6cd2d96ed&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
+          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>17/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -11072,171 +11072,171 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>08/09/2025 05:38</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11248,61 +11248,61 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>08/09/2025 05:38</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a8038b4e1f8e14b2827eddd7c9&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e1ce1545b594a864a4447d576d&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -11336,39 +11336,39 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>26/08/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>26/08/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11380,237 +11380,237 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>22/08/2025 04:00</t>
+          <t>19/08/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>19/08/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bc8a97a404f80b40ea5f8575e2e52&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5bb0e2b2b2404a8b9dc3c6cd2d96ed&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>11/08/2025 04:00</t>
+          <t>06/08/2025 04:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>06/08/2025 04:00</t>
+          <t>02/08/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>02/08/2025 04:00</t>
+          <t>01/08/2025 21:12</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>01/08/2025 21:12</t>
+          <t>01/08/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>01/08/2025 04:00</t>
+          <t>31/07/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>31/07/2025 04:00</t>
+          <t>29/07/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11622,37 +11622,15 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
+          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>29/07/2025 04:00</t>
+          <t>24/07/2025 04:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>CMOC</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>24/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8yaU9FRkxwRUQwT09aeHp0VFMzekRwYzF2RmhZYjE5Zkx5ZksyU2FpcEZNZXVOSGE3Qy1JeDBRcmFJX0ZsOGYyQUNyb2VyT2xfemNGUGpLWmN4d3JVYTB1c0Y4NW1heDVUdk9LWXhB0gFzQVVfeXFMUEVzSzlPZ2ZNRmNiU3A4NEQzR2QtMDhrY3hOaGdzUEttWDlFam9YRzNVSHFPZzlSakxqbHNZRHJsaXlCc0F2YVhxRWkzNnNiZHB3dm1QZ3dUMEJKaHBPajlNM0lBdm9tMjBlbjlLUzdKS21uQQ?oc=5</t>
         </is>
